--- a/Design Files/Balancer-v7.0.2/BOM/Balancer-v7.0.2.xlsx
+++ b/Design Files/Balancer-v7.0.2/BOM/Balancer-v7.0.2.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark Consultants\gerholdvoorde-dronebms\Design Files\Balancer-v1.0\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\gerholdvoorde-dronebms\Design Files\Balancer-v7.0.2\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E66CC674-93C1-4E77-B0F6-B52D22F10ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{D7D46BC0-C817-4026-8F8B-D2FEED907855}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140"/>
   </bookViews>
   <sheets>
     <sheet name="Balancer-v1.0" sheetId="1" r:id="rId1"/>
@@ -18,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Balancer-v1.0'!$1:$1</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="67">
   <si>
     <t>Designator</t>
   </si>
@@ -135,21 +134,6 @@
     <t>Header CON 2.5mm</t>
   </si>
   <si>
-    <t>PS1, PS2</t>
-  </si>
-  <si>
-    <t>Will only be pads on PCB for Welding. Not CELL holder</t>
-  </si>
-  <si>
-    <t>3.7V</t>
-  </si>
-  <si>
-    <t>18650 CELL PAD</t>
-  </si>
-  <si>
-    <t>18650 CELL</t>
-  </si>
-  <si>
     <t>R1, R2</t>
   </si>
   <si>
@@ -228,21 +212,6 @@
     <t>RES-2512</t>
   </si>
   <si>
-    <t>RT1, RT2</t>
-  </si>
-  <si>
-    <t>NTC Thermister 10K</t>
-  </si>
-  <si>
-    <t>DNP NTC 10K</t>
-  </si>
-  <si>
-    <t>Thermistor</t>
-  </si>
-  <si>
-    <t>Thermister</t>
-  </si>
-  <si>
     <t>U1</t>
   </si>
   <si>
@@ -256,12 +225,6 @@
   </si>
   <si>
     <t>TDFN-14-EP(3x3)</t>
-  </si>
-  <si>
-    <t>Do not place (DNP) Component</t>
-  </si>
-  <si>
-    <t>Cell Pads</t>
   </si>
   <si>
     <t>Connector used by client (No part number)</t>
@@ -270,7 +233,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -646,8 +609,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C43E22C-D6B5-4E4B-AD8E-1FD10D815C25}">
-  <dimension ref="A1:I14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" customWidth="1"/>
@@ -815,85 +778,87 @@
         <v>34</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
+      <c r="B7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="D7" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F7" s="4">
         <v>2</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="I7" s="4"/>
+    </row>
+    <row r="8" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F8" s="4">
         <v>2</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="4">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="4">
-        <v>2</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="H9" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I9" s="4"/>
     </row>
@@ -902,7 +867,7 @@
         <v>51</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>52</v>
@@ -917,7 +882,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>52</v>
@@ -926,10 +891,10 @@
     </row>
     <row r="11" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>57</v>
@@ -944,28 +909,28 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>57</v>
       </c>
       <c r="I11" s="4"/>
     </row>
-    <row r="12" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="F12" s="4">
         <v>1</v>
@@ -974,61 +939,9 @@
         <v>65</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I12" s="4"/>
-    </row>
-    <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F13" s="4">
-        <v>2</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F14" s="4">
-        <v>1</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I14" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
